--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/160.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/160.xlsx
@@ -426,13 +426,13 @@
         <v>-1.201890674907266</v>
       </c>
       <c r="E2">
-        <v>-14.92199867460857</v>
+        <v>-13.46964460476457</v>
       </c>
       <c r="F2">
-        <v>-0.9114983607549577</v>
+        <v>-1.06430646718198</v>
       </c>
       <c r="G2">
-        <v>-7.124036928627866</v>
+        <v>-6.895241815863295</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.110417288227544</v>
       </c>
       <c r="E3">
-        <v>-14.37772138362667</v>
+        <v>-14.45052566024799</v>
       </c>
       <c r="F3">
-        <v>-0.9857465878026831</v>
+        <v>-1.153840557913564</v>
       </c>
       <c r="G3">
-        <v>-7.200004017117521</v>
+        <v>-6.883462894834567</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.116994668626106</v>
       </c>
       <c r="E4">
-        <v>-14.47451298706662</v>
+        <v>-14.68879132016156</v>
       </c>
       <c r="F4">
-        <v>-1.110523569686373</v>
+        <v>-1.035932398533888</v>
       </c>
       <c r="G4">
-        <v>-7.301435821895251</v>
+        <v>-6.792432824141228</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.085888584643139</v>
       </c>
       <c r="E5">
-        <v>-15.89472394840418</v>
+        <v>-15.0889770966934</v>
       </c>
       <c r="F5">
-        <v>-1.214829936312081</v>
+        <v>-0.7195358122998116</v>
       </c>
       <c r="G5">
-        <v>-7.667439805080456</v>
+        <v>-6.81567947491799</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.99720678473225</v>
       </c>
       <c r="E6">
-        <v>-15.45610048449524</v>
+        <v>-16.44519166335457</v>
       </c>
       <c r="F6">
-        <v>-1.548362130640468</v>
+        <v>-0.5937233711626226</v>
       </c>
       <c r="G6">
-        <v>-6.930300493124176</v>
+        <v>-6.911867375561514</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.78637358992297</v>
       </c>
       <c r="E7">
-        <v>-15.9430880508061</v>
+        <v>-16.01663499716468</v>
       </c>
       <c r="F7">
-        <v>-1.143896835610359</v>
+        <v>-0.5564186735449497</v>
       </c>
       <c r="G7">
-        <v>-6.634973346656872</v>
+        <v>-6.943436737824004</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.416006342216598</v>
       </c>
       <c r="E8">
-        <v>-17.41656745189589</v>
+        <v>-16.96785001942385</v>
       </c>
       <c r="F8">
-        <v>-0.9134765021128429</v>
+        <v>-0.5251560877632964</v>
       </c>
       <c r="G8">
-        <v>-6.902952076424257</v>
+        <v>-5.935104156381708</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.838087622640444</v>
       </c>
       <c r="E9">
-        <v>-18.12482531516954</v>
+        <v>-18.57998223768049</v>
       </c>
       <c r="F9">
-        <v>-1.32170507025387</v>
+        <v>-0.4589322557464898</v>
       </c>
       <c r="G9">
-        <v>-5.781077714621576</v>
+        <v>-6.316541902870995</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.021065316073575</v>
       </c>
       <c r="E10">
-        <v>-17.71466783887281</v>
+        <v>-18.55539262381884</v>
       </c>
       <c r="F10">
-        <v>-1.130920460245505</v>
+        <v>-0.6861012471880179</v>
       </c>
       <c r="G10">
-        <v>-5.651999544045393</v>
+        <v>-5.759972986808722</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.939089797128616</v>
       </c>
       <c r="E11">
-        <v>-18.51823196611189</v>
+        <v>-19.28428221467144</v>
       </c>
       <c r="F11">
-        <v>-1.121396720215519</v>
+        <v>-0.2772224106357931</v>
       </c>
       <c r="G11">
-        <v>-6.463265281171493</v>
+        <v>-5.689114070086162</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.579285423154428</v>
       </c>
       <c r="E12">
-        <v>-19.36547322515496</v>
+        <v>-20.38554822317477</v>
       </c>
       <c r="F12">
-        <v>-0.7581476736791021</v>
+        <v>-0.446648395530376</v>
       </c>
       <c r="G12">
-        <v>-5.598335600853806</v>
+        <v>-5.134700319169956</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.944383174436983</v>
       </c>
       <c r="E13">
-        <v>-20.30089745854939</v>
+        <v>-20.59522562667792</v>
       </c>
       <c r="F13">
-        <v>-0.7310791120578226</v>
+        <v>-0.1877877239925445</v>
       </c>
       <c r="G13">
-        <v>-4.040581571168524</v>
+        <v>-4.509089975886183</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.05420070731522</v>
       </c>
       <c r="E14">
-        <v>-21.31734062041504</v>
+        <v>-21.35068377453352</v>
       </c>
       <c r="F14">
-        <v>-0.8065881142926088</v>
+        <v>-0.02838001446741881</v>
       </c>
       <c r="G14">
-        <v>-4.547336708501383</v>
+        <v>-4.436837319491589</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.942423117573891</v>
       </c>
       <c r="E15">
-        <v>-22.30590196781547</v>
+        <v>-21.87932424476693</v>
       </c>
       <c r="F15">
-        <v>-0.9584941286179821</v>
+        <v>-0.2640480554616698</v>
       </c>
       <c r="G15">
-        <v>-2.850039873790281</v>
+        <v>-2.5649654868581</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.661798780930702</v>
       </c>
       <c r="E16">
-        <v>-23.32596338041326</v>
+        <v>-22.79792066874886</v>
       </c>
       <c r="F16">
-        <v>-0.07747569369653991</v>
+        <v>0.5929502098807952</v>
       </c>
       <c r="G16">
-        <v>-4.816285428111774</v>
+        <v>-2.825276993156533</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.267188165760409</v>
       </c>
       <c r="E17">
-        <v>-23.35475088968002</v>
+        <v>-23.38163643986356</v>
       </c>
       <c r="F17">
-        <v>-0.45391980459215</v>
+        <v>0.1104369665263195</v>
       </c>
       <c r="G17">
-        <v>-2.582825880042468</v>
+        <v>-2.83719164655237</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.1871561236059836</v>
       </c>
       <c r="E18">
-        <v>-24.98641441633174</v>
+        <v>-25.48749006528047</v>
       </c>
       <c r="F18">
-        <v>-0.2645210532486683</v>
+        <v>0.1246169597274415</v>
       </c>
       <c r="G18">
-        <v>-2.545429957630861</v>
+        <v>-2.706663457029985</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.638449175821091</v>
       </c>
       <c r="E19">
-        <v>-25.83357416284267</v>
+        <v>-24.6678181559961</v>
       </c>
       <c r="F19">
-        <v>-0.2759235305482035</v>
+        <v>0.4151494305439093</v>
       </c>
       <c r="G19">
-        <v>-2.288882541610579</v>
+        <v>-1.323007706709435</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.035181053591774</v>
       </c>
       <c r="E20">
-        <v>-26.09591319058102</v>
+        <v>-26.16458749890734</v>
       </c>
       <c r="F20">
-        <v>0.01527908949712913</v>
+        <v>1.113410963957516</v>
       </c>
       <c r="G20">
-        <v>-1.670535535239968</v>
+        <v>-1.054764133298909</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.334214907180255</v>
       </c>
       <c r="E21">
-        <v>-26.49474042491055</v>
+        <v>-27.07898602748415</v>
       </c>
       <c r="F21">
-        <v>0.6386222466341459</v>
+        <v>1.090162004430545</v>
       </c>
       <c r="G21">
-        <v>-2.2986883774979</v>
+        <v>-1.960297654655757</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.490720296616252</v>
       </c>
       <c r="E22">
-        <v>-26.56826020042508</v>
+        <v>-27.48882198212634</v>
       </c>
       <c r="F22">
-        <v>0.3507836266115821</v>
+        <v>0.8718706264448195</v>
       </c>
       <c r="G22">
-        <v>-0.9250503379791853</v>
+        <v>-1.647550417560808</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.473956984930677</v>
       </c>
       <c r="E23">
-        <v>-27.40294400104488</v>
+        <v>-28.05961348842315</v>
       </c>
       <c r="F23">
-        <v>0.4408984028925291</v>
+        <v>1.164408574743465</v>
       </c>
       <c r="G23">
-        <v>-1.523802225302851</v>
+        <v>-0.9271790187609368</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.262635695197848</v>
       </c>
       <c r="E24">
-        <v>-28.76286738791832</v>
+        <v>-27.45004465919865</v>
       </c>
       <c r="F24">
-        <v>1.205987648159583</v>
+        <v>1.372385121829531</v>
       </c>
       <c r="G24">
-        <v>-1.214726383210953</v>
+        <v>-1.756838146903228</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.837111676177735</v>
       </c>
       <c r="E25">
-        <v>-28.99529584483601</v>
+        <v>-29.2012191433868</v>
       </c>
       <c r="F25">
-        <v>0.5567149345801364</v>
+        <v>1.602162642222475</v>
       </c>
       <c r="G25">
-        <v>-1.074806175993657</v>
+        <v>-0.5240240935340308</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.191213595328092</v>
       </c>
       <c r="E26">
-        <v>-29.04690233462742</v>
+        <v>-28.766811688779</v>
       </c>
       <c r="F26">
-        <v>0.4904795054196907</v>
+        <v>1.699038553245071</v>
       </c>
       <c r="G26">
-        <v>-0.5251364368352259</v>
+        <v>-0.3315291126075684</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.326164215605107</v>
       </c>
       <c r="E27">
-        <v>-28.52099706269464</v>
+        <v>-30.05169146863434</v>
       </c>
       <c r="F27">
-        <v>0.8956679651924437</v>
+        <v>1.697511043754309</v>
       </c>
       <c r="G27">
-        <v>-1.311530045324782</v>
+        <v>-0.9666771375899813</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>8.24751814355106</v>
       </c>
       <c r="E28">
-        <v>-29.64267290355054</v>
+        <v>-29.50769267880391</v>
       </c>
       <c r="F28">
-        <v>1.143498924762</v>
+        <v>0.9937814571148227</v>
       </c>
       <c r="G28">
-        <v>-1.724984077724361</v>
+        <v>-0.9536534514384885</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.96916076834292</v>
       </c>
       <c r="E29">
-        <v>-26.5654389611183</v>
+        <v>-29.14344034352294</v>
       </c>
       <c r="F29">
-        <v>0.6485800511831987</v>
+        <v>1.45578349520858</v>
       </c>
       <c r="G29">
-        <v>-1.248659474988483</v>
+        <v>-1.018877819653209</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>7.507760138840634</v>
       </c>
       <c r="E30">
-        <v>-28.71709357264879</v>
+        <v>-27.98275169909096</v>
       </c>
       <c r="F30">
-        <v>0.8591237088505407</v>
+        <v>1.319578356635868</v>
       </c>
       <c r="G30">
-        <v>-1.734578038697169</v>
+        <v>-0.9909037098463678</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.885887896285063</v>
       </c>
       <c r="E31">
-        <v>-27.78762881104846</v>
+        <v>-28.30879729916921</v>
       </c>
       <c r="F31">
-        <v>0.8062473607950427</v>
+        <v>1.314734064064297</v>
       </c>
       <c r="G31">
-        <v>-1.776612035409295</v>
+        <v>-0.5764896192404007</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.127432353129097</v>
       </c>
       <c r="E32">
-        <v>-29.24446607016006</v>
+        <v>-28.32124154574229</v>
       </c>
       <c r="F32">
-        <v>0.7365485275234923</v>
+        <v>1.200286823693517</v>
       </c>
       <c r="G32">
-        <v>-0.9680874299897108</v>
+        <v>-1.558771517834172</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.257107924650515</v>
       </c>
       <c r="E33">
-        <v>-27.75303126962985</v>
+        <v>-28.6093521190583</v>
       </c>
       <c r="F33">
-        <v>1.427120326336911</v>
+        <v>1.092600718064387</v>
       </c>
       <c r="G33">
-        <v>-0.8030534243115028</v>
+        <v>-1.269681439162855</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.308198727323849</v>
       </c>
       <c r="E34">
-        <v>-27.4912764150385</v>
+        <v>-28.34420543743519</v>
       </c>
       <c r="F34">
-        <v>0.5425233442353753</v>
+        <v>1.011177172573612</v>
       </c>
       <c r="G34">
-        <v>-2.426356255674354</v>
+        <v>-1.69459989076493</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.308324619253434</v>
       </c>
       <c r="E35">
-        <v>-26.08968201034646</v>
+        <v>-26.08119112158208</v>
       </c>
       <c r="F35">
-        <v>1.615257474125929</v>
+        <v>1.786078429726827</v>
       </c>
       <c r="G35">
-        <v>-3.713261312609704</v>
+        <v>-1.879659386410189</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.282932924181379</v>
       </c>
       <c r="E36">
-        <v>-25.92012235807726</v>
+        <v>-26.91048150965874</v>
       </c>
       <c r="F36">
-        <v>0.9600569634120493</v>
+        <v>1.683395663210606</v>
       </c>
       <c r="G36">
-        <v>-1.922802415877971</v>
+        <v>-2.730565595823523</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.263885059385601</v>
       </c>
       <c r="E37">
-        <v>-26.13147076848925</v>
+        <v>-26.98838484801269</v>
       </c>
       <c r="F37">
-        <v>1.432113725040987</v>
+        <v>1.652997892997475</v>
       </c>
       <c r="G37">
-        <v>-2.867592386239497</v>
+        <v>-1.566067960202726</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.2716951177431925</v>
       </c>
       <c r="E38">
-        <v>-26.46992891582253</v>
+        <v>-26.55373738428248</v>
       </c>
       <c r="F38">
-        <v>0.8899969619528783</v>
+        <v>1.771966362652734</v>
       </c>
       <c r="G38">
-        <v>-1.809353330792687</v>
+        <v>-1.977936241288994</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.6732411306554017</v>
       </c>
       <c r="E39">
-        <v>-24.89074134597169</v>
+        <v>-25.94233452308488</v>
       </c>
       <c r="F39">
-        <v>1.439738018616353</v>
+        <v>1.63315352349601</v>
       </c>
       <c r="G39">
-        <v>-2.698814153556373</v>
+        <v>-2.342218740793777</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.546269465338101</v>
       </c>
       <c r="E40">
-        <v>-24.34311298422411</v>
+        <v>-25.4929378195117</v>
       </c>
       <c r="F40">
-        <v>1.490263459982706</v>
+        <v>1.443232072321362</v>
       </c>
       <c r="G40">
-        <v>-2.275911824187715</v>
+        <v>-2.766296313828877</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.335598618850189</v>
       </c>
       <c r="E41">
-        <v>-21.75580105925971</v>
+        <v>-23.77878361033625</v>
       </c>
       <c r="F41">
-        <v>1.094360170427933</v>
+        <v>1.615610358639522</v>
       </c>
       <c r="G41">
-        <v>-4.322981037304975</v>
+        <v>-3.109199310241047</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.027516600344855</v>
       </c>
       <c r="E42">
-        <v>-23.53458564947262</v>
+        <v>-22.63951917643456</v>
       </c>
       <c r="F42">
-        <v>1.160964223082624</v>
+        <v>1.444779462629791</v>
       </c>
       <c r="G42">
-        <v>-3.309828301557499</v>
+        <v>-3.009131450225497</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.612496656313509</v>
       </c>
       <c r="E43">
-        <v>-20.80955830146096</v>
+        <v>-23.06039555070744</v>
       </c>
       <c r="F43">
-        <v>0.817306065622416</v>
+        <v>1.84805522206948</v>
       </c>
       <c r="G43">
-        <v>-2.641717174640563</v>
+        <v>-3.139500733561996</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.091172280788637</v>
       </c>
       <c r="E44">
-        <v>-21.97804497813415</v>
+        <v>-21.82647695309742</v>
       </c>
       <c r="F44">
-        <v>1.743497031753321</v>
+        <v>1.882995759119563</v>
       </c>
       <c r="G44">
-        <v>-2.750260031236647</v>
+        <v>-3.716287151232597</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.461759025409692</v>
       </c>
       <c r="E45">
-        <v>-21.18780362142563</v>
+        <v>-21.91851818730332</v>
       </c>
       <c r="F45">
-        <v>1.47366463396541</v>
+        <v>1.722721577291109</v>
       </c>
       <c r="G45">
-        <v>-2.616643102726123</v>
+        <v>-2.609449287269287</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.731564775305564</v>
       </c>
       <c r="E46">
-        <v>-20.98531290617265</v>
+        <v>-20.7966521505391</v>
       </c>
       <c r="F46">
-        <v>1.768301665262749</v>
+        <v>1.72523981419562</v>
       </c>
       <c r="G46">
-        <v>-3.137951398249617</v>
+        <v>-2.252016306485255</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.912691599032978</v>
       </c>
       <c r="E47">
-        <v>-19.29967449782351</v>
+        <v>-21.07730432716447</v>
       </c>
       <c r="F47">
-        <v>1.077844181150917</v>
+        <v>1.780760311000854</v>
       </c>
       <c r="G47">
-        <v>-3.514986119171674</v>
+        <v>-3.593508948817647</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.014517414618531</v>
       </c>
       <c r="E48">
-        <v>-17.97542642918249</v>
+        <v>-20.55247683204551</v>
       </c>
       <c r="F48">
-        <v>1.930469494974003</v>
+        <v>1.377179712356935</v>
       </c>
       <c r="G48">
-        <v>-3.693136506276474</v>
+        <v>-3.447795286906626</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.055359325121402</v>
       </c>
       <c r="E49">
-        <v>-18.92691768835613</v>
+        <v>-19.17639132143869</v>
       </c>
       <c r="F49">
-        <v>1.360395332041411</v>
+        <v>1.608802835323316</v>
       </c>
       <c r="G49">
-        <v>-3.741708830428661</v>
+        <v>-3.112652209238507</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.051800617113094</v>
       </c>
       <c r="E50">
-        <v>-15.52281396357624</v>
+        <v>-18.41731492285096</v>
       </c>
       <c r="F50">
-        <v>2.055021160924131</v>
+        <v>1.728163951127502</v>
       </c>
       <c r="G50">
-        <v>-2.746403245683397</v>
+        <v>-3.664281791356187</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.018406659030896</v>
       </c>
       <c r="E51">
-        <v>-18.78206539027278</v>
+        <v>-18.24167352998946</v>
       </c>
       <c r="F51">
-        <v>1.747377104668034</v>
+        <v>2.07368593524401</v>
       </c>
       <c r="G51">
-        <v>-4.301091710199313</v>
+        <v>-3.401388059537122</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.977027834562761</v>
       </c>
       <c r="E52">
-        <v>-16.97600127263766</v>
+        <v>-18.02857260013651</v>
       </c>
       <c r="F52">
-        <v>2.041719237169977</v>
+        <v>1.772122095724461</v>
       </c>
       <c r="G52">
-        <v>-3.41407075949807</v>
+        <v>-3.110311653542242</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.941455297704268</v>
       </c>
       <c r="E53">
-        <v>-15.19342182120631</v>
+        <v>-15.59460386201984</v>
       </c>
       <c r="F53">
-        <v>1.773584992557804</v>
+        <v>1.808992728823066</v>
       </c>
       <c r="G53">
-        <v>-4.615838516799982</v>
+        <v>-2.768064145146848</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.924088721227903</v>
       </c>
       <c r="E54">
-        <v>-15.59497066841446</v>
+        <v>-16.24757358613384</v>
       </c>
       <c r="F54">
-        <v>1.310032250686007</v>
+        <v>1.735065908327628</v>
       </c>
       <c r="G54">
-        <v>-4.486810004406887</v>
+        <v>-3.40307974830769</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.940326405518413</v>
       </c>
       <c r="E55">
-        <v>-14.09286678312218</v>
+        <v>-16.08701654019189</v>
       </c>
       <c r="F55">
-        <v>1.457364020213121</v>
+        <v>2.065001331393059</v>
       </c>
       <c r="G55">
-        <v>-4.069558776273765</v>
+        <v>-4.539676106123509</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.993777358263285</v>
       </c>
       <c r="E56">
-        <v>-14.70041138446525</v>
+        <v>-15.4231920638815</v>
       </c>
       <c r="F56">
-        <v>1.80327699374375</v>
+        <v>1.470536718652439</v>
       </c>
       <c r="G56">
-        <v>-4.555666041078189</v>
+        <v>-4.431441130262577</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.089625940846171</v>
       </c>
       <c r="E57">
-        <v>-15.65240530425374</v>
+        <v>-13.77853181682776</v>
       </c>
       <c r="F57">
-        <v>1.618458285770347</v>
+        <v>1.677829034263793</v>
       </c>
       <c r="G57">
-        <v>-4.481794527914892</v>
+        <v>-4.865162322453574</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.231762651944609</v>
       </c>
       <c r="E58">
-        <v>-13.41090576841107</v>
+        <v>-15.00352026369465</v>
       </c>
       <c r="F58">
-        <v>1.481375077750668</v>
+        <v>1.697603820903423</v>
       </c>
       <c r="G58">
-        <v>-4.50319720482628</v>
+        <v>-5.039806841832286</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.410357787536796</v>
       </c>
       <c r="E59">
-        <v>-14.06435098229588</v>
+        <v>-12.920838839775</v>
       </c>
       <c r="F59">
-        <v>1.7696187694332</v>
+        <v>1.531564201951484</v>
       </c>
       <c r="G59">
-        <v>-6.323037193219045</v>
+        <v>-5.698943079792258</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.620543892594782</v>
       </c>
       <c r="E60">
-        <v>-12.23245644892101</v>
+        <v>-13.09803349922113</v>
       </c>
       <c r="F60">
-        <v>1.63062368944786</v>
+        <v>1.781156270619392</v>
       </c>
       <c r="G60">
-        <v>-6.128747896610297</v>
+        <v>-4.858028096816445</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.853107087108868</v>
       </c>
       <c r="E61">
-        <v>-13.54037031181636</v>
+        <v>-12.98452276974486</v>
       </c>
       <c r="F61">
-        <v>1.324525366765387</v>
+        <v>2.03459196403629</v>
       </c>
       <c r="G61">
-        <v>-5.390049317705021</v>
+        <v>-5.850956709864512</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.087105752044637</v>
       </c>
       <c r="E62">
-        <v>-12.04844643609333</v>
+        <v>-12.15119751132737</v>
       </c>
       <c r="F62">
-        <v>1.290824067349892</v>
+        <v>1.530033378991111</v>
       </c>
       <c r="G62">
-        <v>-5.675825540291528</v>
+        <v>-5.206088923178799</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.311326730389567</v>
       </c>
       <c r="E63">
-        <v>-12.16176696966128</v>
+        <v>-11.81163441633622</v>
       </c>
       <c r="F63">
-        <v>1.321597916363894</v>
+        <v>1.500699232523174</v>
       </c>
       <c r="G63">
-        <v>-5.239085130568715</v>
+        <v>-5.633728643214155</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.509471236393164</v>
       </c>
       <c r="E64">
-        <v>-12.26316403116702</v>
+        <v>-10.94226703329168</v>
       </c>
       <c r="F64">
-        <v>1.921012852703644</v>
+        <v>1.199102258307514</v>
       </c>
       <c r="G64">
-        <v>-5.281410455288298</v>
+        <v>-5.628921731091133</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.65861056836675</v>
       </c>
       <c r="E65">
-        <v>-11.54761079626701</v>
+        <v>-11.98745241968402</v>
       </c>
       <c r="F65">
-        <v>1.885678012769828</v>
+        <v>1.858802460753401</v>
       </c>
       <c r="G65">
-        <v>-5.509692433494282</v>
+        <v>-5.740096471390938</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.748434828825097</v>
       </c>
       <c r="E66">
-        <v>-11.99667692123765</v>
+        <v>-12.6975579003528</v>
       </c>
       <c r="F66">
-        <v>1.086714339300094</v>
+        <v>1.088894602304262</v>
       </c>
       <c r="G66">
-        <v>-5.55057767090428</v>
+        <v>-5.57774731814508</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.764870568909036</v>
       </c>
       <c r="E67">
-        <v>-9.156594634113095</v>
+        <v>-10.89469088536709</v>
       </c>
       <c r="F67">
-        <v>1.416170966006707</v>
+        <v>0.9527010608751897</v>
       </c>
       <c r="G67">
-        <v>-5.409498772748239</v>
+        <v>-5.558532911835149</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.694228556047015</v>
       </c>
       <c r="E68">
-        <v>-11.99931249311011</v>
+        <v>-11.16581515268033</v>
       </c>
       <c r="F68">
-        <v>1.527303080031484</v>
+        <v>1.147756733212389</v>
       </c>
       <c r="G68">
-        <v>-5.612090917569478</v>
+        <v>-5.505299339563669</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.535275192986884</v>
       </c>
       <c r="E69">
-        <v>-11.81382166928192</v>
+        <v>-11.28408983681266</v>
       </c>
       <c r="F69">
-        <v>1.163031828120012</v>
+        <v>1.142634109193477</v>
       </c>
       <c r="G69">
-        <v>-5.157288171384403</v>
+        <v>-5.788658863906507</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.283874234530627</v>
       </c>
       <c r="E70">
-        <v>-11.55916746193459</v>
+        <v>-10.75614675157643</v>
       </c>
       <c r="F70">
-        <v>1.289465544809301</v>
+        <v>0.7664492772949432</v>
       </c>
       <c r="G70">
-        <v>-6.156334672589044</v>
+        <v>-6.751140389629898</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.941053730812841</v>
       </c>
       <c r="E71">
-        <v>-10.94646040022278</v>
+        <v>-10.91860122812759</v>
       </c>
       <c r="F71">
-        <v>0.7544545173024064</v>
+        <v>0.7827051592074807</v>
       </c>
       <c r="G71">
-        <v>-6.475918186222588</v>
+        <v>-5.558754718386281</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.515805001399817</v>
       </c>
       <c r="E72">
-        <v>-11.180971955184</v>
+        <v>-11.4627064370972</v>
       </c>
       <c r="F72">
-        <v>1.289448977461245</v>
+        <v>0.6608730234407434</v>
       </c>
       <c r="G72">
-        <v>-5.458756379827055</v>
+        <v>-6.138646427772718</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.013873447612628</v>
       </c>
       <c r="E73">
-        <v>-11.15925339384321</v>
+        <v>-11.65099585786213</v>
       </c>
       <c r="F73">
-        <v>0.5869553149867351</v>
+        <v>0.6026586758416054</v>
       </c>
       <c r="G73">
-        <v>-4.861970956553717</v>
+        <v>-5.731571816627315</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.448328365319121</v>
       </c>
       <c r="E74">
-        <v>-11.14102175748833</v>
+        <v>-11.99012421934855</v>
       </c>
       <c r="F74">
-        <v>0.3787037499229394</v>
+        <v>0.31806559930321</v>
       </c>
       <c r="G74">
-        <v>-5.719759790143195</v>
+        <v>-5.673872318423357</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.835319902951978</v>
       </c>
       <c r="E75">
-        <v>-12.35660456384129</v>
+        <v>-12.03294999803908</v>
       </c>
       <c r="F75">
-        <v>0.4402754706056239</v>
+        <v>0.5173335198836451</v>
       </c>
       <c r="G75">
-        <v>-5.122663175589166</v>
+        <v>-5.451612222553308</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.187144022525589</v>
       </c>
       <c r="E76">
-        <v>-11.91914038927831</v>
+        <v>-11.15869186306626</v>
       </c>
       <c r="F76">
-        <v>0.7813731444237791</v>
+        <v>0.665341237211444</v>
       </c>
       <c r="G76">
-        <v>-5.884677926727528</v>
+        <v>-5.39468408146</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.52302316330323</v>
       </c>
       <c r="E77">
-        <v>-13.88379166666205</v>
+        <v>-13.19189517997811</v>
       </c>
       <c r="F77">
-        <v>-0.1893823312429335</v>
+        <v>0.04854466765875168</v>
       </c>
       <c r="G77">
-        <v>-4.474365663724767</v>
+        <v>-5.292365050477746</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.858807152769004</v>
       </c>
       <c r="E78">
-        <v>-13.63077223843148</v>
+        <v>-12.8339962937299</v>
       </c>
       <c r="F78">
-        <v>0.006258168480642512</v>
+        <v>0.2480420460097622</v>
       </c>
       <c r="G78">
-        <v>-4.688127589195508</v>
+        <v>-4.898277709482904</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.205528703730091</v>
       </c>
       <c r="E79">
-        <v>-14.09139050059568</v>
+        <v>-12.85471406231499</v>
       </c>
       <c r="F79">
-        <v>-0.2693015615302242</v>
+        <v>0.1514635188847707</v>
       </c>
       <c r="G79">
-        <v>-4.150511546345563</v>
+        <v>-4.535170453644561</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.5800601393245363</v>
       </c>
       <c r="E80">
-        <v>-14.79947175338304</v>
+        <v>-14.33452879854151</v>
       </c>
       <c r="F80">
-        <v>-0.329636529680529</v>
+        <v>0.2418152082429183</v>
       </c>
       <c r="G80">
-        <v>-3.9851862126599</v>
+        <v>-4.688412296111886</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.008107661145521807</v>
       </c>
       <c r="E81">
-        <v>-14.88347494622532</v>
+        <v>-14.24464311796326</v>
       </c>
       <c r="F81">
-        <v>-0.4393016050349472</v>
+        <v>0.1151437501090263</v>
       </c>
       <c r="G81">
-        <v>-3.995293308191295</v>
+        <v>-4.06154394552319</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.553904395754121</v>
       </c>
       <c r="E82">
-        <v>-17.44067251903872</v>
+        <v>-13.7937837172856</v>
       </c>
       <c r="F82">
-        <v>0.7119311050470966</v>
+        <v>0.1195813142858233</v>
       </c>
       <c r="G82">
-        <v>-4.059633760747031</v>
+        <v>-3.749902430638357</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.04790521577333</v>
       </c>
       <c r="E83">
-        <v>-16.03755654708011</v>
+        <v>-16.6687352542692</v>
       </c>
       <c r="F83">
-        <v>-0.1398219379008419</v>
+        <v>-0.01212578928968691</v>
       </c>
       <c r="G83">
-        <v>-3.74730034184449</v>
+        <v>-2.625733860776962</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.488666763370369</v>
       </c>
       <c r="E84">
-        <v>-17.17794857100971</v>
+        <v>-17.91386635352222</v>
       </c>
       <c r="F84">
-        <v>-0.2375005369367512</v>
+        <v>-0.3149769117531862</v>
       </c>
       <c r="G84">
-        <v>-3.478599913149544</v>
+        <v>-3.605685135311087</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.876482328941093</v>
       </c>
       <c r="E85">
-        <v>-18.60909126860179</v>
+        <v>-18.11964021243076</v>
       </c>
       <c r="F85">
-        <v>-0.2134447475594536</v>
+        <v>-0.5312594987871231</v>
       </c>
       <c r="G85">
-        <v>-4.061424765883776</v>
+        <v>-2.644696665625907</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.207724451575042</v>
       </c>
       <c r="E86">
-        <v>-18.11049269493526</v>
+        <v>-18.3012682479304</v>
       </c>
       <c r="F86">
-        <v>-0.8571789966837829</v>
+        <v>-0.5948449806260131</v>
       </c>
       <c r="G86">
-        <v>-4.00176542472057</v>
+        <v>-2.898449981211044</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.483712296242261</v>
       </c>
       <c r="E87">
-        <v>-22.24039306282052</v>
+        <v>-20.7899817083258</v>
       </c>
       <c r="F87">
-        <v>-0.5798705830856065</v>
+        <v>-0.7586803139191022</v>
       </c>
       <c r="G87">
-        <v>-2.458971750327254</v>
+        <v>-2.646027504932694</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.704233928502693</v>
       </c>
       <c r="E88">
-        <v>-21.07258565724847</v>
+        <v>-21.90563015027749</v>
       </c>
       <c r="F88">
-        <v>-0.7175593276767319</v>
+        <v>-0.846387026160111</v>
       </c>
       <c r="G88">
-        <v>-2.325632907642029</v>
+        <v>-2.458773117594898</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.865906208593081</v>
       </c>
       <c r="E89">
-        <v>-22.6305709117954</v>
+        <v>-23.55336975965644</v>
       </c>
       <c r="F89">
-        <v>-1.263329191011186</v>
+        <v>-0.9863032506973644</v>
       </c>
       <c r="G89">
-        <v>-1.825942474489975</v>
+        <v>-3.037787532413429</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.96644859499636</v>
       </c>
       <c r="E90">
-        <v>-24.19324313694026</v>
+        <v>-24.40129028980066</v>
       </c>
       <c r="F90">
-        <v>-1.068124412541483</v>
+        <v>-1.355354182522989</v>
       </c>
       <c r="G90">
-        <v>-3.467694976143185</v>
+        <v>-2.169818771290691</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.001483311802996</v>
       </c>
       <c r="E91">
-        <v>-26.64083352487201</v>
+        <v>-25.57835842471838</v>
       </c>
       <c r="F91">
-        <v>-0.9202492339981317</v>
+        <v>-0.7781428060478766</v>
       </c>
       <c r="G91">
-        <v>-3.82524713656663</v>
+        <v>-3.463748805860374</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.965537755997089</v>
       </c>
       <c r="E92">
-        <v>-28.02529671239302</v>
+        <v>-26.94662778918796</v>
       </c>
       <c r="F92">
-        <v>-1.798070170744768</v>
+        <v>-1.737785733006034</v>
       </c>
       <c r="G92">
-        <v>-3.408724228452147</v>
+        <v>-3.191108827973695</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.853471067635116</v>
       </c>
       <c r="E93">
-        <v>-29.17255390291825</v>
+        <v>-28.29788367681073</v>
       </c>
       <c r="F93">
-        <v>-1.978843132322898</v>
+        <v>-1.838410006526298</v>
       </c>
       <c r="G93">
-        <v>-3.28465822382242</v>
+        <v>-3.093917832031772</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.66222470726416</v>
       </c>
       <c r="E94">
-        <v>-31.95941982774166</v>
+        <v>-31.32188087880879</v>
       </c>
       <c r="F94">
-        <v>-1.973006455602773</v>
+        <v>-1.528173988666841</v>
       </c>
       <c r="G94">
-        <v>-3.414802390062249</v>
+        <v>-3.241468846717088</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.393318702859178</v>
       </c>
       <c r="E95">
-        <v>-33.67868894830877</v>
+        <v>-32.5495365968662</v>
       </c>
       <c r="F95">
-        <v>-1.445522802685118</v>
+        <v>-1.934576006684696</v>
       </c>
       <c r="G95">
-        <v>-3.157083040921066</v>
+        <v>-3.871826512304176</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.047135594574129</v>
       </c>
       <c r="E96">
-        <v>-35.19451637408129</v>
+        <v>-36.35489934651775</v>
       </c>
       <c r="F96">
-        <v>-2.27050715301159</v>
+        <v>-2.050707317985367</v>
       </c>
       <c r="G96">
-        <v>-3.451887121193165</v>
+        <v>-3.667440051800651</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.637577426070254</v>
       </c>
       <c r="E97">
-        <v>-38.38536293665496</v>
+        <v>-37.30462676506541</v>
       </c>
       <c r="F97">
-        <v>-2.570227046692507</v>
+        <v>-2.050415732659581</v>
       </c>
       <c r="G97">
-        <v>-3.446252572685325</v>
+        <v>-3.561661500729858</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.169841557678279</v>
       </c>
       <c r="E98">
-        <v>-39.38736705914717</v>
+        <v>-39.32032300146361</v>
       </c>
       <c r="F98">
-        <v>-2.193063912891267</v>
+        <v>-2.125551141195705</v>
       </c>
       <c r="G98">
-        <v>-4.09751633335291</v>
+        <v>-4.236161980537588</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.6739829691103116</v>
       </c>
       <c r="E99">
-        <v>-42.72787515920034</v>
+        <v>-40.25213124836291</v>
       </c>
       <c r="F99">
-        <v>-2.538172541673778</v>
+        <v>-2.263919147057126</v>
       </c>
       <c r="G99">
-        <v>-3.264328163665756</v>
+        <v>-4.695198914467391</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.150998630004458</v>
       </c>
       <c r="E100">
-        <v>-43.17706128873218</v>
+        <v>-43.70505192294549</v>
       </c>
       <c r="F100">
-        <v>-2.414096358612857</v>
+        <v>-2.425153406705424</v>
       </c>
       <c r="G100">
-        <v>-4.912076063290586</v>
+        <v>-5.316972335471148</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.3409124616782664</v>
       </c>
       <c r="E101">
-        <v>-46.62713808163794</v>
+        <v>-45.65145797855232</v>
       </c>
       <c r="F101">
-        <v>-2.28160313437209</v>
+        <v>-2.224943632388006</v>
       </c>
       <c r="G101">
-        <v>-5.09207042426076</v>
+        <v>-5.390122149706885</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.8355258092007569</v>
       </c>
       <c r="E102">
-        <v>-47.73325182156648</v>
+        <v>-47.09815824859776</v>
       </c>
       <c r="F102">
-        <v>-2.886947524581079</v>
+        <v>-2.707838753115173</v>
       </c>
       <c r="G102">
-        <v>-4.122116997255235</v>
+        <v>-5.319859131181393</v>
       </c>
     </row>
   </sheetData>
